--- a/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-3 壓力　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下6-3 壓力　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>壓力的公式是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>垂直力</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>面積小</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>P=F/A</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>力除面積</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>壓力的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>受力面積</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>P=F/A</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>帕斯卡Pa</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>N/m²</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>力相同面積越小壓力？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>P=F/A</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>垂直力</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>集中</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>力相同面積越大壓力？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>面積小壓力大</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>減小壓力</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>越小</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分散</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>刀刃磨利是為了？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>面積小壓力大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>帕斯卡Pa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>增大壓力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>減小壓力</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>減面積</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>雪鞋面積大是為了？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>減小壓力</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>面積小</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>較小</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>防陷</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>圖釘尖端壓力大因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>較小</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>站立</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>面積小</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>集中</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>壓力是單位面積的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>垂直力</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>帕斯卡Pa</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>減小壓力</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>面積小</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>受力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>壓力等於力除以？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>面積小</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>垂直力</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>受力面積</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>公式</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>壓力的SI單位是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>面積小</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>減小壓力</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>帕斯卡Pa</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>較小</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-3 壓力　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下6-3 壓力　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>力20N作用面積4m²,壓力？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>5 Pa</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>24 N</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>6 Pa</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>20/4</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>壓力10Pa作用面積2m²,力？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>20 N</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>100 N</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>24 N</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>6 N</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>P×A</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>同一人站立與躺下地面壓力誰大？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>P=F/A</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>帕斯卡Pa</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>站立</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>面積小</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>寬輪胎車輛對地壓力？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>P=F/A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>較小</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>帕斯卡Pa</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>面積大</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>力40N面積8m²壓力？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>6 N</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>300 Pa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>6 Pa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>5 Pa</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>40/8</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>書包用寬背帶為了？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>帕斯卡Pa</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>減小壓力</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>面積小壓力大</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>分散</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>釘子做尖是為了？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>增大壓力易釘入</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>分散重量降低壓力</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>減小對地壓力避免陷入</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>減面積</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>壓力2Pa面積3m²的力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>6 N</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>24 N</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>100 N</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>P×A</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>力30N面積5m²壓力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>6 Pa</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>24 N</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>5 Pa</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>30/5</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>壓力8Pa面積3m²的力？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>6 N</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>100 N</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>24 N</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>P×A</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-3 壓力　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下6-3 壓力　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>同樣體重,高跟鞋比平底鞋對地壓力?為何</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>減小刃面積增大壓力易切</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力易釘入</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>減小對地壓力避免陷入</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>大,受力面積小</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用P=F/A解釋為何雪地用雪橇不易陷？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>增大面積減小壓力</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>增大力或減小接觸面積</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>減小對地壓力避免陷入</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>力60N壓在0.2m²,壓力多少Pa？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>100 N</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>300 Pa</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>5 Pa</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>60/0.2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>切菜前磨刀原理是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>減小刃面積增大壓力易切</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>分散重量降低壓力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>增大面積減壓力防陷</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>減面積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>駱駝腳掌寬大在沙漠的作用？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>減小刃面積增大壓力易切</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>增大面積減小壓力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>增大面積減壓力防陷</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>要對地施加更大壓力應如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>增大力或減小接觸面積</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>減小對地壓力避免陷入</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>分散重量降低壓力</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>策略</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>壓力250Pa面積0.4m²的總力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>100 N</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>20 N</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>24 N</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>6 N</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>P×A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>推土機用寬履帶原因用壓力解釋？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>增大壓力易釘入</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>減小對地壓力避免陷入</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>增大面積減壓力防陷</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何釘子做成尖的較易釘入？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>增大壓力</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>站立</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>面積小壓力大</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>受力面積</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>減面積</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>大象腳掌寬大對地面壓力的影響？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>增大面積減小壓力</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>增大壓力易釘入</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>分散重量降低壓力</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>大,受力面積小</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>力除面積</t>
+          <t>力除面積：壓力的定義是垂直作用力除以受力面積，公式寫作P=F/A</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>N/m²</t>
+          <t>N/m²：壓力的單位是帕斯卡(Pa)，換算成基本單位就是牛頓每平方公尺(N/m²)</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>集中</t>
+          <t>集中：施力大小不變時，接觸面積越小，力越集中在小範圍內，壓力就越大</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分散</t>
+          <t>分散：施力大小不變時，接觸面積越大，力分散在較大範圍內，壓力就越小</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>減面積</t>
+          <t>減面積：把刀刃磨得很薄很尖，能大幅減少接觸面積，在相同施力下產生很大的壓力，更容易切開物體</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防陷</t>
+          <t>防陷：雪鞋接觸面積做得很大，可以把體重分散在較大範圍，減小對雪地的壓力，避免陷入鬆軟的雪中</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>集中</t>
+          <t>集中：圖釘尖端非常細小，接觸面積極小，即使施力不大，產生的壓力也很集中很大，因此容易刺入物體</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>受力</t>
+          <t>受力：壓力的定義是單位面積上所承受的垂直作用力大小</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>公式</t>
+          <t>公式：壓力的定義是垂直作用力除以受力面積，公式寫作P=F/A</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：國際單位制中，壓力的單位是帕斯卡，符號寫作Pa</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>20/4</t>
+          <t>20/4：壓力=力÷面積，20牛頓除以4平方公尺等於5帕斯卡</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>P×A</t>
+          <t>P×A：力=壓力×面積，10帕斯卡乘以2平方公尺等於20牛頓</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>面積小</t>
+          <t>面積小：站立時腳掌接觸地面的面積比躺下時全身接觸地面的面積小很多，體重(力)相同下接觸面積越小壓力越大，所以站立時壓力較大</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>面積大</t>
+          <t>面積大：寬輪胎和地面的接觸面積比窄輪胎大，車重相同下接觸面積越大壓力越小，所以寬輪胎對地壓力較小</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>40/8</t>
+          <t>40/8：壓力=力÷面積，40牛頓除以8平方公尺等於5帕斯卡</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分散</t>
+          <t>分散：把肩帶做寬，能增加和肩膀接觸的面積，讓書包重量分散在較大範圍，減小肩膀承受的壓力，背起來比較不會痛</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>減面積</t>
+          <t>減面積：把釘子尖端做得很細小，能大幅減少接觸面積，在相同施力下產生很大的壓力，更容易釘入物體</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>P×A</t>
+          <t>P×A：力=壓力×面積，2帕斯卡乘以3平方公尺等於6牛頓</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>30/5</t>
+          <t>30/5：壓力=力÷面積，30牛頓除以5平方公尺等於6帕斯卡</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>P×A</t>
+          <t>P×A：力=壓力×面積，8帕斯卡乘以3平方公尺等於24牛頓</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：高跟鞋鞋跟接觸地面的面積遠比平底鞋小，體重(力)相同的情況下，接觸面積越小壓力越大，所以高跟鞋對地面的壓力比平底鞋大</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：雪橇的接觸面積比一般鞋底大很多，根據P=F/A，體重(F)固定時面積(A)增大，壓力(P)就會變小，所以踩雪橇比較不容易陷入雪中</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>60/0.2</t>
+          <t>60/0.2：壓力=力÷面積，60牛頓除以0.2平方公尺等於300帕斯卡</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>減面積</t>
+          <t>減面積：磨刀能讓刀刃變得更薄更銳利，接觸食材的面積更小，相同施力下產生的壓力更大，因此更容易切開食材</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應：駱駝寬大的腳掌能把體重分散在較大的接觸面積上，減小對沙地的壓力，避免走在鬆軟的沙漠中時陷下去，這是對沙漠環境的適應</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>策略</t>
+          <t>策略：根據P=F/A，要增大壓力可以增加施力(F)，或是減小接觸面積(A)，兩種方式都能達到提高壓力的效果</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>P×A</t>
+          <t>P×A：力=壓力×面積，250帕斯卡乘以0.4平方公尺等於100牛頓</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>設計：推土機本身很重，用寬履帶大幅增加接觸地面的面積，根據P=F/A，面積增大能有效減小對地面的壓力，避免沉重的機身陷入鬆軟的地面</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>減面積</t>
+          <t>減面積：在相同的施力下，接觸面積越小，產生的壓力就越大，釘子做成尖的可以大幅減少接觸面積，讓局部壓力變得很大，因此容易釘入物體</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>面積：大象體重雖然很重，但腳掌面積寬大，同樣的重量分散在較大的接觸面積上，單位面積受到的壓力反而比較小，不容易陷入鬆軟的地面</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-3_三種難度測驗卷.xlsx
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>減小壓力</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>較小</t>
+          <t>站立</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>站立</t>
+          <t>帕斯卡Pa</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>站立</t>
+          <t>P=F/A</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>受力面積</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
